--- a/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week01_01Sep.xlsx
+++ b/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week01_01Sep.xlsx
@@ -202,7 +202,7 @@
     <t xml:space="preserve">Tiered 3 ways at every step — scaffold, task version and evidence prompt (symbol-supported → sentence-stem → independent): same outcome, different rung. Hands-on route first; easy-read/symbol resources; chunked steps with modelling; movement built into every session.  Nothing is written in week 1 — pointing, feeling and sorting only. Regulation before content.</t>
   </si>
   <si>
-    <t xml:space="preserve">TA scribes the tick sheet so no pupil sees a blank page. Teacher names every part aloud each time it is touched — repetition is the method. LOOP [Feedback Policy]: Voice = point/say/sort [VF, ?] → Audience: name one body part back; [R] once received → EVIDENCE: circuit photos + tick sheet, upload same day [E: science — daily EFL; banks ELC 8939].</t>
+    <t xml:space="preserve">TA scribes the tick sheet so no pupil sees a blank page. Teacher names every part aloud each time it is touched — repetition is the method. LOOP [Feedback Policy]: Voice = point/say/sort [VF, ?] → Audience: name one body part back; [R] once received → EVIDENCE: circuit photos + tick sheet, upload same day [E: science — daily evidence platform; banks ELC 8939].</t>
   </si>
   <si>
     <t xml:space="preserve">Note who can already name a bone vs who names only 'arm/leg'.  → Influence: sets the starting rung for W2–W8 and the ELC 8939 taster decision [NS].</t>
@@ -229,7 +229,7 @@
     <t xml:space="preserve">Tiered 3 ways at every step — scaffold, task version and evidence prompt (symbol-supported → sentence-stem → independent): same outcome, different rung. Hands-on route first; easy-read/symbol resources; chunked steps with modelling; movement built into every session.  Pictures or words both count on the hand; sharing always opt-out; bingo can be done with the TA in a pair.  Pupil A: choice of task &amp; seat, own table, quiet-space option, short 10–20-min goals, opt-out of group sharing. Pupil B: colourblind-safe — labels/patterns/position, never colour alone; movement; offer choice with a reason, not commands. Pupil C: fatigue-aware — soft re-entry after rest, TA checks understanding (he may tick at random), scribe/photo instead of writing. Pupil D: middle seat, fidget/scribble pad, short 10-min bursts, answer or visibly 'park' his questions.</t>
   </si>
   <si>
-    <t xml:space="preserve">TA co-runs bingo, scribes finger labels and keeps a quiet space open.  LOOP [Feedback Policy]: Voice = build/choose/say [VF] → Audience: name the choice back; [R] when a strength is shown for real that week → EVIDENCE: hand photo + clip, same day [E: identity/communication — daily EFL; banks AQA UAS].</t>
+    <t xml:space="preserve">TA co-runs bingo, scribes finger labels and keeps a quiet space open.  LOOP [Feedback Policy]: Voice = build/choose/say [VF] → Audience: name the choice back; [R] when a strength is shown for real that week → EVIDENCE: hand photo + clip, same day [E: identity/communication — daily evidence platform; banks AQA UAS].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: what pupils value about themselves feeds the whole-child profile and the W2 charter — record the change made [NS].</t>
@@ -256,7 +256,7 @@
     <t xml:space="preserve">Tiered 3 ways at every step — scaffold, task version and evidence prompt (symbol-supported → sentence-stem → independent): same outcome, different rung. Hands-on route first; easy-read/symbol resources; chunked steps with modelling; movement built into every session.  Symbol cards carry the name in words too — never symbol or colour alone; pointing counts as answering on the first rung.  Pupil A: choice of task &amp; seat, own table, quiet-space option, short 10–20-min goals, opt-out of group sharing. Pupil B: colourblind-safe — labels/patterns/position, never colour alone; movement; offer choice with a reason, not commands. Pupil C: fatigue-aware — soft re-entry after rest, TA checks understanding (he may tick at random), scribe/photo instead of writing. Pupil D: middle seat, fidget/scribble pad, short 10-min bursts, answer or visibly 'park' his questions.</t>
   </si>
   <si>
-    <t xml:space="preserve">TA models respectful artefact handling and supports the map match.  LOOP [Feedback Policy]: Voice = place/point/say [VF, ?] → Audience: name the match back; [R] once received → EVIDENCE: map photo + scribed line, same day [E: cultural/community — daily EFL].</t>
+    <t xml:space="preserve">TA models respectful artefact handling and supports the map match.  LOOP [Feedback Policy]: Voice = place/point/say [VF, ?] → Audience: name the match back; [R] once received → EVIDENCE: map photo + scribed line, same day [E: cultural/community — daily evidence platform].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: which faiths pupils recognise shapes W2's belief→action pairs and the artefact choices — record the change made [NS].</t>
@@ -283,7 +283,7 @@
     <t xml:space="preserve">Tiered 3 ways at every step — scaffold, task version and evidence prompt (symbol-supported → sentence-stem → independent): same outcome, different rung. Hands-on route first; easy-read/symbol resources; chunked steps with modelling; movement built into every session.  3-card strips on the first rung, 5-card + date cards on the top rung; the physical line means no reading load.  Pupil A: choice of task &amp; seat, own table, quiet-space option, short 10–20-min goals, opt-out of group sharing. Pupil B: colourblind-safe — labels/patterns/position, never colour alone; movement; offer choice with a reason, not commands. Pupil C: fatigue-aware — soft re-entry after rest, TA checks understanding (he may tick at random), scribe/photo instead of writing. Pupil D: middle seat, fidget/scribble pad, short 10-min bursts, answer or visibly 'park' his questions.</t>
   </si>
   <si>
-    <t xml:space="preserve">TA anchors one end of the human timeline and prompts the story call-out.  LOOP [Feedback Policy]: Voice = order/place/say [VF, I] → Audience: name the order back ('Romans, then…'); [R] on an accurate re-do → EVIDENCE: strip photo, same day [E: humanities — daily EFL; banks AQA UAS].</t>
+    <t xml:space="preserve">TA anchors one end of the human timeline and prompts the story call-out.  LOOP [Feedback Policy]: Voice = order/place/say [VF, I] → Audience: name the order back ('Romans, then…'); [R] on an accurate re-do → EVIDENCE: strip photo, same day [E: humanities — daily evidence platform; banks AQA UAS].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: who sequences unprompted vs with the line shapes W2's detective stations and the APDR target — record the change made [NS].</t>
